--- a/templates/Roofing_CRM_Google_Sheets_TEMPLATE.xlsx
+++ b/templates/Roofing_CRM_Google_Sheets_TEMPLATE.xlsx
@@ -73,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -81,6 +81,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -461,14 +462,11 @@
     <col width="32" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,40 +532,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Lead Score</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Last Contact</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Urgency</t>
+          <t>Follow-up Count</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Assigned To</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Last Contact</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Follow-up Count</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Assigned To</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -581,7 +564,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01T09:14:00Z</t>
+          <t>2026-06-01T09:14:00.000-04:00</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -630,40 +613,27 @@
           <t>Weekday mornings</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
-        <v>86</v>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Booked</t>
+        </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Emergency</t>
-        </is>
+          <t>2026-06-01T09:20:00.000-04:00</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Booked</t>
+          <t>J. Reyes</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01T09:20:00Z</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>J. Reyes</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>Example row — replace with real data. Active leak, scored Hot/Emergency by AI scoring (workflow 02).</t>
+          <t>Example row — replace with real data.</t>
         </is>
       </c>
     </row>
@@ -675,7 +645,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02T14:02:00Z</t>
+          <t>2026-06-02T14:02:00.000-04:00</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -704,24 +674,17 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="n">
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>Example row — missed-call auto-SMS sent (workflow 03); no Lead record is normally created for pure missed calls — this row illustrates what a follow-up form submission from the same number would look like once captured.</t>
         </is>
@@ -730,13 +693,13 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SOURCE OF TRUTH: matches the live CRM Adapter sub-workflow contract exactly (workflow 01, id wVRHChyFrUNRaH4M) — verified against production data. 'Lead ID' and 'Phone' are the match keys; new leads get LEAD-#### minted by the adapter. Do not rename/remove columns — every workflow that scores, follows up, reminds, or reports on leads depends on these exact header names.</t>
+          <t>SOURCE OF TRUTH: matches the live CRM Adapter sub-workflow contract exactly (workflow 01, id wVRHChyFrUNRaH4M) — verified against production data. 'Lead ID' and 'Phone' are the match keys; new leads get LEAD-#### minted by the adapter. Do not rename/remove columns — every workflow that follows up, reminds, or reports on leads depends on these exact header names. V1.1 (2026-06-11): 'Lead Score', 'Temperature', and 'Urgency' columns were removed system-wide — AI lead scoring was removed; every lead now follows the same 'Every Lead Alert' notification path (see docs/V1_1_RECONCILIATION.md). All timestamps are ISO 8601 in America/New_York (Boston time), the system-wide default timezone.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:T5"/>
+    <mergeCell ref="A5:Q5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1629,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1665,7 +1628,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — replace with e.g. =COUNTIFS(Leads!P:P,"&lt;&gt;Booked",Leads!P:P,"&lt;&gt;Lost") once real data exists.</t>
+          <t>PLACEHOLDER — replace with e.g. =COUNTIFS(Leads!M:M,"&lt;&gt;Booked",Leads!M:M,"&lt;&gt;Lost") once real data exists. ('Status' is column M in the V1.1 17-column Leads schema.)</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1650,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Hot/Emergency Leads (Open)</t>
+          <t>Appointments This Week</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
@@ -1695,14 +1658,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — e.g. =COUNTIFS(Leads!N:N,"Hot",Leads!P:P,"&lt;&gt;Booked")  (combine with an OR for Urgency="Emergency" via SUMPRODUCT if needed)</t>
+          <t>PLACEHOLDER — e.g. =COUNTIFS(Appointments!G:G, "&gt;="&amp;TEXT(TODAY()-7,"YYYY-MM-DD"))</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Appointments This Week</t>
+          <t>Jobs Completed This Month</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -1710,14 +1673,14 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — e.g. =COUNTIFS(Appointments!G:G, "&gt;="&amp;TEXT(TODAY()-7,"YYYY-MM-DD"))</t>
+          <t>PLACEHOLDER — depends on the Jobs tab going live first (see that tab's note); e.g. =COUNTIFS(Jobs!I:I,"Completed",Jobs!K:K,"&gt;="&amp;EOMONTH(TODAY(),-1)+1)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Jobs Completed This Month</t>
+          <t>Stale Leads (No Contact 7+ Days)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1725,35 +1688,23 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — depends on the Jobs tab going live first (see that tab's note); e.g. =COUNTIFS(Jobs!I:I,"Completed",Jobs!K:K,"&gt;="&amp;EOMONTH(TODAY(),-1)+1)</t>
+          <t>PLACEHOLDER — mirrors workflow 07's own 'Stale' definition; e.g. =COUNTIFS(Leads!N:N,"&lt;"&amp;TEXT(TODAY()-7,"YYYY-MM-DD"))  — keep this formula in sync with whatever workflow 07 (Pipeline Status Digest) uses internally so the dashboard never disagrees with its email digest. ('Last Contact' is column N in the V1.1 17-column Leads schema.)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Stale Leads (No Contact 7+ Days)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — mirrors workflow 07's own 'Stale' definition; e.g. =COUNTIFS(Leads!Q:Q,"&lt;"&amp;TEXT(TODAY()-7,"YYYY-MM-DD"))  — keep this formula in sync with whatever workflow 07 (Pipeline Status Digest) uses internally so the dashboard never disagrees with the SMS digest</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ THIS TAB IS A SUMMARY VIEW, NOT A DATA-ENTRY TAB — it is meant to hold live formulas that reference the other tabs, not raw rows. No workflow currently writes to or reads from it; the system's owner-facing reporting is delivered instead via SMS digests (workflows 07/08) and (as of 2026-06-07) Workflow 11's health alerts. The 'Value' column above is intentionally left at 0/placeholder — replace each with a live formula (see the Notes column for a starting point per metric) once the sheet has real rows to compute against. Keep every formula's definition of a status ('Stale', 'Hot', etc.) in sync with the corresponding live workflow's own definition — a Dashboard that disagrees with the SMS digest the owner already trusts is worse than no Dashboard at all.</t>
+      <c r="B7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ THIS TAB IS A SUMMARY VIEW, NOT A DATA-ENTRY TAB — it is meant to hold live formulas that reference the other tabs, not raw rows. No workflow currently writes to or reads from it; the system's owner-facing reporting is delivered instead via email digests (workflows 07/08, converted from SMS to email in V1.1) and Workflow 11's health alerts. The 'Value' column above is intentionally left at 0/placeholder — replace each with a live formula (see the Notes column for a starting point per metric) once the sheet has real rows to compute against. Keep every formula's definition of a status ('Stale', etc.) in sync with the corresponding live workflow's own definition — a Dashboard that disagrees with the email digest the owner already trusts is worse than no Dashboard at all. V1.1 (2026-06-11): the 'Hot/Emergency Leads (Open)' metric was removed along with AI lead scoring system-wide.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A8:C8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/Roofing_CRM_Google_Sheets_TEMPLATE.xlsx
+++ b/templates/Roofing_CRM_Google_Sheets_TEMPLATE.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -729,6 +729,8 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -805,6 +807,16 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Notified Appt Date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Notified Appt Time</t>
         </is>
       </c>
     </row>
@@ -868,17 +880,27 @@
           <t>Example row — booked via owner-facing form (workflow 06).</t>
         </is>
       </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>SOURCE OF TRUTH: matches the exact column set written by workflow 06's 'Write Appointment' node (live, verified) — 15 columns. 'Appt Date' must stay 'YYYY-MM-DD' and 'Appt Time' must stay 'H:MM AM/PM' — both workflow 09 (Reminders) and workflow 11 (Health Monitor) parse these with strict regexes. 'Reminder 24h'/'Reminder 2h' are write-only flag columns — leave them blank; the system manages them. 'Team Approval' and 'Calendar Event ID' are reserved for future phases (crew-approval workflow, calendar sync) — currently always blank.</t>
+          <t>SOURCE OF TRUTH: matches the exact column set written by workflow 06's 'Write Appointment' node (live, verified) — 17 columns. 'Appt Date' must stay 'YYYY-MM-DD' and 'Appt Time' must stay 'H:MM AM/PM' — workflows 09 (Reminders), 11 (Health Monitor), and 13 (Reschedule Notifier) parse these with strict regexes. 'Reminder 24h'/'Reminder 2h' are write-only flag columns — leave them blank; the system manages them. 'Team Approval' and 'Calendar Event ID' are reserved for future phases (crew-approval workflow, calendar sync) — currently always blank. 'Notified Appt Date'/'Notified Appt Time' (added 2026-06-12) should be seeded equal to 'Appt Date'/'Appt Time' at booking time — workflow 13 compares against these to detect owner-initiated reschedules and notify the customer.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A4:Q4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/Roofing_CRM_Google_Sheets_TEMPLATE.xlsx
+++ b/templates/Roofing_CRM_Google_Sheets_TEMPLATE.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -731,6 +731,9 @@
     <col width="40" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -817,6 +820,21 @@
       <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notified Appt Time</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Notify Customer</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Reschedule Status</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Reschedule Attempts</t>
         </is>
       </c>
     </row>
@@ -890,18 +908,36 @@
           <t>10:00 AM</t>
         </is>
       </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>SOURCE OF TRUTH: matches the exact column set written by workflow 06's 'Write Appointment' node (live, verified) — 17 columns. 'Appt Date' must stay 'YYYY-MM-DD' and 'Appt Time' must stay 'H:MM AM/PM' — workflows 09 (Reminders), 11 (Health Monitor), and 13 (Reschedule Notifier) parse these with strict regexes. 'Reminder 24h'/'Reminder 2h' are write-only flag columns — leave them blank; the system manages them. 'Team Approval' and 'Calendar Event ID' are reserved for future phases (crew-approval workflow, calendar sync) — currently always blank. 'Notified Appt Date'/'Notified Appt Time' (added 2026-06-12) should be seeded equal to 'Appt Date'/'Appt Time' at booking time — workflow 13 compares against these to detect owner-initiated reschedules and notify the customer.</t>
+          <t>SOURCE OF TRUTH: matches the exact column set written by workflow 06's 'Write Appointment' node (live, verified) — 20 columns. 'Appt Date' must stay 'YYYY-MM-DD' and 'Appt Time' must stay 'H:MM AM/PM' — workflows 09 (Reminders), 11 (Health Monitor), and 13 (Reschedule Notifier) parse these with strict regexes. 'Reminder 24h'/'Reminder 2h' are write-only flag columns — leave them blank; the system manages them. 'Team Approval' and 'Calendar Event ID' are reserved for future phases (crew-approval workflow, calendar sync) — currently always blank. 'Notified Appt Date'/'Notified Appt Time' (added 2026-06-12) should be seeded equal to 'Appt Date'/'Appt Time' at booking time — workflow 13 compares against these to detect owner-initiated reschedules and notify the customer. 'Notify Customer' (added 2026-06-13) is a dropdown defaulting to 'No' — the owner picks 'Send Update' to trigger workflow 13's reschedule-notification flow; workflow 13 resets it back to 'No' after a successful run so the field can be reused for another notification later. 'Reschedule Status' ('None'/'Pending Customer Confirmation'/'Confirmed'/'Escalated to Owner') and 'Reschedule Attempts' (0-2) track the YES/NO customer-confirmation flow and the two-attempt escalation rule — both managed by workflow 13 and reset to 'None'/0 on each new notification cycle.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A4:T4"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="R2:R200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Please select 'No' or 'Send Update' from the dropdown." type="list" errorStyle="stop">
+      <formula1>"No,Send Update"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
